--- a/BOM/20220119 BOM TeKaDe Baseboard 5VEXT.xlsx
+++ b/BOM/20220119 BOM TeKaDe Baseboard 5VEXT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IngBuero\Projekte_Kunden\2021_TeKaDeRevival\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1A26E7-C4B3-4AB7-8AE7-569667D0FA22}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC6119B-F1A2-40B4-8942-298856A4FED1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11960" xr2:uid="{261E8F2A-9F01-4E4B-AED6-14B6866C8B8C}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="514">
   <si>
     <t>SOT-23</t>
   </si>
@@ -1043,9 +1043,6 @@
   </si>
   <si>
     <t>3,5mm</t>
-  </si>
-  <si>
-    <t>Verschiedene Alternativen vorhanden (vermutlich nicht Pinkompatibel)</t>
   </si>
   <si>
     <t>MINI50</t>
@@ -1582,7 +1579,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;€&quot;;[Red]#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1636,13 +1633,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1701,7 +1691,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1743,14 +1733,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="1" fontId="6" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
@@ -1758,6 +1744,9 @@
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Erklärender Text" xfId="1" builtinId="53"/>
@@ -2099,16 +2088,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39" t="s">
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="39"/>
+      <c r="P1" s="42"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -2165,28 +2154,28 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E3" t="s">
         <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G3">
         <v>805</v>
       </c>
       <c r="I3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K3" t="s">
+        <v>391</v>
+      </c>
+      <c r="L3" s="29" t="s">
         <v>392</v>
-      </c>
-      <c r="L3" s="29" t="s">
-        <v>393</v>
       </c>
       <c r="M3" s="16">
         <v>0.152</v>
@@ -2194,11 +2183,11 @@
       <c r="N3" s="16">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="O3" s="42">
+      <c r="O3" s="40">
         <f>B3*M3</f>
         <v>0.152</v>
       </c>
-      <c r="P3" s="42">
+      <c r="P3" s="40">
         <f>B3*N3</f>
         <v>6.0999999999999999E-2</v>
       </c>
@@ -2211,10 +2200,10 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>232</v>
@@ -2231,7 +2220,7 @@
         <v>233</v>
       </c>
       <c r="L4" s="29" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="M4" s="23">
         <v>1.7000000000000001E-2</v>
@@ -2239,11 +2228,11 @@
       <c r="N4" s="23">
         <v>1.4E-2</v>
       </c>
-      <c r="O4" s="42">
+      <c r="O4" s="40">
         <f t="shared" ref="O4:O67" si="0">B4*M4</f>
         <v>0.255</v>
       </c>
-      <c r="P4" s="42">
+      <c r="P4" s="40">
         <f t="shared" ref="P4:P67" si="1">B4*N4</f>
         <v>0.21</v>
       </c>
@@ -2257,7 +2246,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>244</v>
@@ -2266,29 +2255,29 @@
         <v>162</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G5" s="12">
         <v>805</v>
       </c>
       <c r="J5" s="20"/>
       <c r="K5" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="L5" s="29" t="s">
         <v>396</v>
       </c>
-      <c r="L5" s="29" t="s">
-        <v>397</v>
-      </c>
-      <c r="M5" s="40">
+      <c r="M5" s="38">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="38">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="40">
         <f t="shared" si="0"/>
         <v>0.14399999999999999</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="40">
         <f t="shared" si="1"/>
         <v>0.13200000000000001</v>
       </c>
@@ -2301,22 +2290,22 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>162</v>
       </c>
       <c r="F6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G6">
         <v>1210</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L6" s="13">
         <v>1100</v>
@@ -2327,11 +2316,11 @@
       <c r="N6" s="16">
         <v>0.17599999999999999</v>
       </c>
-      <c r="O6" s="42">
+      <c r="O6" s="40">
         <f t="shared" si="0"/>
         <v>1.444</v>
       </c>
-      <c r="P6" s="42">
+      <c r="P6" s="40">
         <f t="shared" si="1"/>
         <v>0.70399999999999996</v>
       </c>
@@ -2344,25 +2333,25 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>162</v>
       </c>
       <c r="F7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G7">
         <v>603</v>
       </c>
       <c r="K7" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="L7" s="29" t="s">
         <v>409</v>
-      </c>
-      <c r="L7" s="29" t="s">
-        <v>410</v>
       </c>
       <c r="M7" s="16">
         <v>1.7999999999999999E-2</v>
@@ -2370,11 +2359,11 @@
       <c r="N7" s="16">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="O7" s="42">
+      <c r="O7" s="40">
         <f t="shared" si="0"/>
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="P7" s="42">
+      <c r="P7" s="40">
         <f t="shared" si="1"/>
         <v>2.1999999999999999E-2</v>
       </c>
@@ -2387,7 +2376,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D8" t="s">
         <v>68</v>
@@ -2396,13 +2385,13 @@
         <v>84</v>
       </c>
       <c r="F8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L8" s="13">
         <v>825</v>
@@ -2413,11 +2402,11 @@
       <c r="N8" s="16">
         <v>0.12</v>
       </c>
-      <c r="O8" s="42">
+      <c r="O8" s="40">
         <f t="shared" si="0"/>
         <v>0.186</v>
       </c>
-      <c r="P8" s="42">
+      <c r="P8" s="40">
         <f t="shared" si="1"/>
         <v>0.12</v>
       </c>
@@ -2430,7 +2419,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D9" t="s">
         <v>245</v>
@@ -2439,16 +2428,16 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G9">
         <v>1206</v>
       </c>
       <c r="K9" t="s">
+        <v>425</v>
+      </c>
+      <c r="L9" s="29" t="s">
         <v>426</v>
-      </c>
-      <c r="L9" s="29" t="s">
-        <v>427</v>
       </c>
       <c r="M9" s="16">
         <v>0.28399999999999997</v>
@@ -2456,11 +2445,11 @@
       <c r="N9" s="16">
         <v>0.153</v>
       </c>
-      <c r="O9" s="42">
+      <c r="O9" s="40">
         <f t="shared" si="0"/>
         <v>0.56799999999999995</v>
       </c>
-      <c r="P9" s="42">
+      <c r="P9" s="40">
         <f t="shared" si="1"/>
         <v>0.30599999999999999</v>
       </c>
@@ -2473,16 +2462,16 @@
         <v>2</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G10" s="9">
         <v>805</v>
@@ -2491,10 +2480,10 @@
       <c r="I10" s="9"/>
       <c r="J10" s="20"/>
       <c r="K10" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M10" s="25">
         <v>0.16800000000000001</v>
@@ -2502,11 +2491,11 @@
       <c r="N10" s="25">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="O10" s="42">
+      <c r="O10" s="40">
         <f t="shared" si="0"/>
         <v>0.33600000000000002</v>
       </c>
-      <c r="P10" s="42">
+      <c r="P10" s="40">
         <f t="shared" si="1"/>
         <v>0.13400000000000001</v>
       </c>
@@ -2531,11 +2520,11 @@
       <c r="L11"/>
       <c r="M11" s="24"/>
       <c r="N11" s="24"/>
-      <c r="O11" s="42">
+      <c r="O11" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P11" s="42">
+      <c r="P11" s="40">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2548,7 +2537,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>247</v>
@@ -2557,32 +2546,32 @@
         <v>86</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G12" s="12">
         <v>603</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J12" s="20"/>
       <c r="K12" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="L12" s="29" t="s">
         <v>416</v>
       </c>
-      <c r="L12" s="29" t="s">
-        <v>417</v>
-      </c>
-      <c r="M12" s="40">
+      <c r="M12" s="38">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="N12" s="40">
+      <c r="N12" s="38">
         <v>3.9E-2</v>
       </c>
-      <c r="O12" s="42">
+      <c r="O12" s="40">
         <f t="shared" si="0"/>
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="P12" s="42">
+      <c r="P12" s="40">
         <f t="shared" si="1"/>
         <v>3.9E-2</v>
       </c>
@@ -2595,7 +2584,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D13" t="s">
         <v>248</v>
@@ -2611,13 +2600,13 @@
       </c>
       <c r="H13" s="7"/>
       <c r="I13" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>231</v>
       </c>
       <c r="L13" s="29" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M13" s="23">
         <v>5.8000000000000003E-2</v>
@@ -2625,11 +2614,11 @@
       <c r="N13" s="23">
         <v>0.2</v>
       </c>
-      <c r="O13" s="42">
+      <c r="O13" s="40">
         <f t="shared" si="0"/>
         <v>0.58000000000000007</v>
       </c>
-      <c r="P13" s="42">
+      <c r="P13" s="40">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -2643,7 +2632,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D14" t="s">
         <v>249</v>
@@ -2652,20 +2641,20 @@
         <v>86</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G14" s="7">
         <v>402</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K14" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="L14" s="29" t="s">
         <v>429</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>430</v>
       </c>
       <c r="M14" s="23">
         <v>2.8000000000000001E-2</v>
@@ -2673,11 +2662,11 @@
       <c r="N14" s="23">
         <v>1.6E-2</v>
       </c>
-      <c r="O14" s="42">
+      <c r="O14" s="40">
         <f t="shared" si="0"/>
         <v>0.53200000000000003</v>
       </c>
-      <c r="P14" s="42">
+      <c r="P14" s="40">
         <f t="shared" si="1"/>
         <v>0.30399999999999999</v>
       </c>
@@ -2692,7 +2681,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>250</v>
@@ -2701,32 +2690,32 @@
         <v>86</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G15" s="12">
         <v>603</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J15" s="20"/>
       <c r="K15" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="L15" s="29" t="s">
         <v>413</v>
       </c>
-      <c r="L15" s="29" t="s">
-        <v>414</v>
-      </c>
-      <c r="M15" s="40">
+      <c r="M15" s="38">
         <v>5.5E-2</v>
       </c>
-      <c r="N15" s="40">
+      <c r="N15" s="38">
         <v>2.4E-2</v>
       </c>
-      <c r="O15" s="42">
+      <c r="O15" s="40">
         <f t="shared" si="0"/>
         <v>5.5E-2</v>
       </c>
-      <c r="P15" s="42">
+      <c r="P15" s="40">
         <f t="shared" si="1"/>
         <v>2.4E-2</v>
       </c>
@@ -2739,7 +2728,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D16" t="s">
         <v>279</v>
@@ -2748,20 +2737,20 @@
         <v>83</v>
       </c>
       <c r="F16" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G16" s="7">
         <v>603</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K16" t="s">
+        <v>449</v>
+      </c>
+      <c r="L16" s="29" t="s">
         <v>450</v>
-      </c>
-      <c r="L16" s="29" t="s">
-        <v>451</v>
       </c>
       <c r="M16" s="16">
         <v>3.9E-2</v>
@@ -2769,11 +2758,11 @@
       <c r="N16" s="16">
         <v>1.6E-2</v>
       </c>
-      <c r="O16" s="42">
+      <c r="O16" s="40">
         <f t="shared" si="0"/>
         <v>0.156</v>
       </c>
-      <c r="P16" s="42">
+      <c r="P16" s="40">
         <f t="shared" si="1"/>
         <v>6.4000000000000001E-2</v>
       </c>
@@ -2786,7 +2775,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D17" t="s">
         <v>23</v>
@@ -2795,20 +2784,20 @@
         <v>83</v>
       </c>
       <c r="F17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G17" s="7">
         <v>603</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K17" t="s">
+        <v>437</v>
+      </c>
+      <c r="L17" s="29" t="s">
         <v>438</v>
-      </c>
-      <c r="L17" s="29" t="s">
-        <v>439</v>
       </c>
       <c r="M17" s="16">
         <v>1.9E-2</v>
@@ -2816,11 +2805,11 @@
       <c r="N17" s="16">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="O17" s="42">
+      <c r="O17" s="40">
         <f t="shared" si="0"/>
         <v>1.9E-2</v>
       </c>
-      <c r="P17" s="42">
+      <c r="P17" s="40">
         <f t="shared" si="1"/>
         <v>5.0000000000000001E-3</v>
       </c>
@@ -2833,7 +2822,7 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D18" t="s">
         <v>276</v>
@@ -2842,20 +2831,20 @@
         <v>83</v>
       </c>
       <c r="F18" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G18" s="7">
         <v>402</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K18" t="s">
+        <v>463</v>
+      </c>
+      <c r="L18" s="29" t="s">
         <v>464</v>
-      </c>
-      <c r="L18" s="29" t="s">
-        <v>465</v>
       </c>
       <c r="M18" s="16">
         <v>1.4999999999999999E-2</v>
@@ -2863,11 +2852,11 @@
       <c r="N18" s="16">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="O18" s="42">
+      <c r="O18" s="40">
         <f t="shared" si="0"/>
         <v>0.105</v>
       </c>
-      <c r="P18" s="42">
+      <c r="P18" s="40">
         <f t="shared" si="1"/>
         <v>2.8000000000000001E-2</v>
       </c>
@@ -2880,29 +2869,29 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F19" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G19" s="7">
         <v>402</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K19" t="s">
+        <v>470</v>
+      </c>
+      <c r="L19" s="29" t="s">
         <v>471</v>
-      </c>
-      <c r="L19" s="29" t="s">
-        <v>472</v>
       </c>
       <c r="M19" s="16">
         <v>1.9E-2</v>
@@ -2910,11 +2899,11 @@
       <c r="N19" s="16">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="O19" s="42">
+      <c r="O19" s="40">
         <f t="shared" si="0"/>
         <v>1.9E-2</v>
       </c>
-      <c r="P19" s="42">
+      <c r="P19" s="40">
         <f t="shared" si="1"/>
         <v>4.0000000000000001E-3</v>
       </c>
@@ -2927,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D20" t="s">
         <v>269</v>
@@ -2936,20 +2925,20 @@
         <v>83</v>
       </c>
       <c r="F20" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G20" s="7">
         <v>402</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K20" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="M20" s="16">
         <v>1.4999999999999999E-2</v>
@@ -2957,11 +2946,11 @@
       <c r="N20" s="16">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="O20" s="42">
+      <c r="O20" s="40">
         <f t="shared" si="0"/>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P20" s="42">
+      <c r="P20" s="40">
         <f t="shared" si="1"/>
         <v>4.0000000000000001E-3</v>
       </c>
@@ -2974,7 +2963,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>270</v>
@@ -2983,33 +2972,33 @@
         <v>83</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G21" s="9">
         <v>402</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J21" s="20"/>
       <c r="K21" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="L21" s="29" t="s">
         <v>494</v>
       </c>
-      <c r="L21" s="29" t="s">
-        <v>495</v>
-      </c>
-      <c r="M21" s="40">
+      <c r="M21" s="38">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="N21" s="40">
+      <c r="N21" s="38">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="O21" s="42">
+      <c r="O21" s="40">
         <f t="shared" si="0"/>
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="P21" s="42">
+      <c r="P21" s="40">
         <f t="shared" si="1"/>
         <v>3.0000000000000001E-3</v>
       </c>
@@ -3022,29 +3011,29 @@
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D22" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F22" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G22" s="7">
         <v>402</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K22" t="s">
+        <v>477</v>
+      </c>
+      <c r="L22" s="29" t="s">
         <v>478</v>
-      </c>
-      <c r="L22" s="29" t="s">
-        <v>479</v>
       </c>
       <c r="M22" s="16">
         <v>1.2999999999999999E-2</v>
@@ -3052,11 +3041,11 @@
       <c r="N22" s="16">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="O22" s="42">
+      <c r="O22" s="40">
         <f t="shared" si="0"/>
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="P22" s="42">
+      <c r="P22" s="40">
         <f t="shared" si="1"/>
         <v>6.0000000000000001E-3</v>
       </c>
@@ -3069,29 +3058,29 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D23" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F23" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G23" s="7">
         <v>603</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K23" t="s">
+        <v>441</v>
+      </c>
+      <c r="L23" s="29" t="s">
         <v>442</v>
-      </c>
-      <c r="L23" s="29" t="s">
-        <v>443</v>
       </c>
       <c r="M23" s="16">
         <v>2.5000000000000001E-2</v>
@@ -3099,11 +3088,11 @@
       <c r="N23" s="16">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="O23" s="42">
+      <c r="O23" s="40">
         <f t="shared" si="0"/>
         <v>7.5000000000000011E-2</v>
       </c>
-      <c r="P23" s="42">
+      <c r="P23" s="40">
         <f t="shared" si="1"/>
         <v>1.2E-2</v>
       </c>
@@ -3116,7 +3105,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D24" t="s">
         <v>271</v>
@@ -3125,20 +3114,20 @@
         <v>83</v>
       </c>
       <c r="F24" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G24" s="7">
         <v>805</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K24" t="s">
+        <v>454</v>
+      </c>
+      <c r="L24" s="29" t="s">
         <v>455</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>456</v>
       </c>
       <c r="M24" s="16">
         <v>3.2000000000000001E-2</v>
@@ -3146,11 +3135,11 @@
       <c r="N24" s="16">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="O24" s="42">
+      <c r="O24" s="40">
         <f t="shared" si="0"/>
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="P24" s="42">
+      <c r="P24" s="40">
         <f t="shared" si="1"/>
         <v>7.0000000000000001E-3</v>
       </c>
@@ -3163,29 +3152,29 @@
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D25" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E25" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F25" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G25" s="7">
         <v>805</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K25" t="s">
+        <v>460</v>
+      </c>
+      <c r="L25" s="29" t="s">
         <v>461</v>
-      </c>
-      <c r="L25" s="29" t="s">
-        <v>462</v>
       </c>
       <c r="M25" s="16">
         <v>3.5000000000000003E-2</v>
@@ -3193,11 +3182,11 @@
       <c r="N25" s="16">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="O25" s="42">
+      <c r="O25" s="40">
         <f t="shared" si="0"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="P25" s="42">
+      <c r="P25" s="40">
         <f t="shared" si="1"/>
         <v>1.4E-2</v>
       </c>
@@ -3210,7 +3199,7 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D26" t="s">
         <v>324</v>
@@ -3219,20 +3208,20 @@
         <v>83</v>
       </c>
       <c r="F26" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G26" s="7">
         <v>402</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K26" t="s">
+        <v>480</v>
+      </c>
+      <c r="L26" s="29" t="s">
         <v>481</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>482</v>
       </c>
       <c r="M26" s="16">
         <v>0.02</v>
@@ -3240,11 +3229,11 @@
       <c r="N26" s="16">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="O26" s="42">
+      <c r="O26" s="40">
         <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
-      <c r="P26" s="42">
+      <c r="P26" s="40">
         <f t="shared" si="1"/>
         <v>2.4E-2</v>
       </c>
@@ -3257,26 +3246,26 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D27" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F27" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G27" s="7">
         <v>603</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K27" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L27" s="13">
         <v>865</v>
@@ -3287,11 +3276,11 @@
       <c r="N27" s="16">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="O27" s="42">
+      <c r="O27" s="40">
         <f t="shared" si="0"/>
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="P27" s="42">
+      <c r="P27" s="40">
         <f t="shared" si="1"/>
         <v>5.0000000000000001E-3</v>
       </c>
@@ -3316,11 +3305,11 @@
       <c r="J28" s="19"/>
       <c r="M28" s="24"/>
       <c r="N28" s="24"/>
-      <c r="O28" s="42">
+      <c r="O28" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P28" s="42">
+      <c r="P28" s="40">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3344,11 +3333,11 @@
       <c r="J29" s="19"/>
       <c r="M29" s="24"/>
       <c r="N29" s="24"/>
-      <c r="O29" s="42">
+      <c r="O29" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P29" s="42">
+      <c r="P29" s="40">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3364,26 +3353,26 @@
         <v>62</v>
       </c>
       <c r="D30" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F30" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G30" s="7">
         <v>603</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K30" t="s">
+        <v>451</v>
+      </c>
+      <c r="L30" s="29" t="s">
         <v>452</v>
-      </c>
-      <c r="L30" s="29" t="s">
-        <v>453</v>
       </c>
       <c r="M30" s="16">
         <v>1.2E-2</v>
@@ -3391,11 +3380,11 @@
       <c r="N30" s="16">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="O30" s="42">
+      <c r="O30" s="40">
         <f t="shared" si="0"/>
         <v>3.6000000000000004E-2</v>
       </c>
-      <c r="P30" s="42">
+      <c r="P30" s="40">
         <f t="shared" si="1"/>
         <v>1.2E-2</v>
       </c>
@@ -3408,7 +3397,7 @@
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D31" t="s">
         <v>277</v>
@@ -3417,20 +3406,20 @@
         <v>83</v>
       </c>
       <c r="F31" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G31" s="7">
         <v>402</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K31" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L31" s="29" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="M31" s="16">
         <v>5.5E-2</v>
@@ -3438,11 +3427,11 @@
       <c r="N31" s="16">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="O31" s="42">
+      <c r="O31" s="40">
         <f t="shared" si="0"/>
         <v>0.22</v>
       </c>
-      <c r="P31" s="42">
+      <c r="P31" s="40">
         <f t="shared" si="1"/>
         <v>4.3999999999999997E-2</v>
       </c>
@@ -3455,7 +3444,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D32" t="s">
         <v>272</v>
@@ -3464,20 +3453,20 @@
         <v>83</v>
       </c>
       <c r="F32" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G32" s="7">
         <v>402</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K32" t="s">
+        <v>483</v>
+      </c>
+      <c r="L32" s="29" t="s">
         <v>484</v>
-      </c>
-      <c r="L32" s="29" t="s">
-        <v>485</v>
       </c>
       <c r="M32" s="16">
         <v>1.9E-2</v>
@@ -3485,11 +3474,11 @@
       <c r="N32" s="16">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="O32" s="42">
+      <c r="O32" s="40">
         <f t="shared" si="0"/>
         <v>1.9E-2</v>
       </c>
-      <c r="P32" s="42">
+      <c r="P32" s="40">
         <f t="shared" si="1"/>
         <v>4.0000000000000001E-3</v>
       </c>
@@ -3502,7 +3491,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D33" t="s">
         <v>273</v>
@@ -3511,20 +3500,20 @@
         <v>83</v>
       </c>
       <c r="F33" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G33" s="7">
         <v>402</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K33" t="s">
+        <v>485</v>
+      </c>
+      <c r="L33" s="29" t="s">
         <v>486</v>
-      </c>
-      <c r="L33" s="29" t="s">
-        <v>487</v>
       </c>
       <c r="M33" s="16">
         <v>1.9E-2</v>
@@ -3532,11 +3521,11 @@
       <c r="N33" s="16">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="O33" s="42">
+      <c r="O33" s="40">
         <f t="shared" si="0"/>
         <v>1.9E-2</v>
       </c>
-      <c r="P33" s="42">
+      <c r="P33" s="40">
         <f t="shared" si="1"/>
         <v>4.0000000000000001E-3</v>
       </c>
@@ -3549,7 +3538,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D34" t="s">
         <v>274</v>
@@ -3558,20 +3547,20 @@
         <v>94</v>
       </c>
       <c r="F34" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G34" s="7">
         <v>402</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K34" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L34" s="29" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M34" s="16">
         <v>8.7999999999999995E-2</v>
@@ -3579,11 +3568,11 @@
       <c r="N34" s="16">
         <v>1.6E-2</v>
       </c>
-      <c r="O34" s="42">
+      <c r="O34" s="40">
         <f t="shared" si="0"/>
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="P34" s="42">
+      <c r="P34" s="40">
         <f t="shared" si="1"/>
         <v>1.6E-2</v>
       </c>
@@ -3605,17 +3594,17 @@
         <v>94</v>
       </c>
       <c r="F35" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G35" s="7">
         <v>603</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K35" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="L35" s="29">
         <v>640</v>
@@ -3626,11 +3615,11 @@
       <c r="N35" s="16">
         <v>0.13400000000000001</v>
       </c>
-      <c r="O35" s="42">
+      <c r="O35" s="40">
         <f t="shared" si="0"/>
         <v>0.22800000000000001</v>
       </c>
-      <c r="P35" s="42">
+      <c r="P35" s="40">
         <f t="shared" si="1"/>
         <v>0.13400000000000001</v>
       </c>
@@ -3652,21 +3641,21 @@
         <v>86</v>
       </c>
       <c r="F36" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G36">
         <v>603</v>
       </c>
       <c r="H36"/>
       <c r="I36" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J36" s="19"/>
       <c r="K36" t="s">
+        <v>502</v>
+      </c>
+      <c r="L36" s="29" t="s">
         <v>503</v>
-      </c>
-      <c r="L36" s="29" t="s">
-        <v>504</v>
       </c>
       <c r="M36" s="16">
         <v>9.7000000000000003E-2</v>
@@ -3674,11 +3663,11 @@
       <c r="N36" s="16">
         <v>0.06</v>
       </c>
-      <c r="O36" s="42">
+      <c r="O36" s="40">
         <f t="shared" si="0"/>
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="P36" s="42">
+      <c r="P36" s="40">
         <f t="shared" si="1"/>
         <v>0.06</v>
       </c>
@@ -3712,7 +3701,7 @@
         <v>192</v>
       </c>
       <c r="L37" s="29" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M37" s="16">
         <v>1.32</v>
@@ -3720,11 +3709,11 @@
       <c r="N37" s="16">
         <v>1.04</v>
       </c>
-      <c r="O37" s="42">
+      <c r="O37" s="40">
         <f t="shared" si="0"/>
         <v>1.32</v>
       </c>
-      <c r="P37" s="42">
+      <c r="P37" s="40">
         <f t="shared" si="1"/>
         <v>1.04</v>
       </c>
@@ -3732,8 +3721,8 @@
     <row r="38" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="43"/>
-      <c r="P38" s="43"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="41"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
@@ -3769,11 +3758,11 @@
       <c r="N39" s="16">
         <v>1.3</v>
       </c>
-      <c r="O39" s="42">
+      <c r="O39" s="40">
         <f t="shared" si="0"/>
         <v>1.45</v>
       </c>
-      <c r="P39" s="42">
+      <c r="P39" s="40">
         <f t="shared" si="1"/>
         <v>1.3</v>
       </c>
@@ -3790,7 +3779,7 @@
         <v>229</v>
       </c>
       <c r="D40" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>87</v>
@@ -3809,7 +3798,7 @@
         <v>228</v>
       </c>
       <c r="L40" s="29" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="M40" s="23">
         <v>1.79</v>
@@ -3817,11 +3806,11 @@
       <c r="N40" s="23">
         <v>0.91500000000000004</v>
       </c>
-      <c r="O40" s="42">
+      <c r="O40" s="40">
         <f t="shared" si="0"/>
         <v>5.37</v>
       </c>
-      <c r="P40" s="42">
+      <c r="P40" s="40">
         <f t="shared" si="1"/>
         <v>2.7450000000000001</v>
       </c>
@@ -3838,7 +3827,7 @@
         <v>213</v>
       </c>
       <c r="D41" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>208</v>
@@ -3864,11 +3853,11 @@
       <c r="N41" s="25">
         <v>1.27</v>
       </c>
-      <c r="O41" s="42">
+      <c r="O41" s="40">
         <f t="shared" si="0"/>
         <v>3.76</v>
       </c>
-      <c r="P41" s="42">
+      <c r="P41" s="40">
         <f t="shared" si="1"/>
         <v>2.54</v>
       </c>
@@ -3909,11 +3898,11 @@
       <c r="N42" s="26">
         <v>0.82599999999999996</v>
       </c>
-      <c r="O42" s="42">
+      <c r="O42" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P42" s="42">
+      <c r="P42" s="40">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3955,11 +3944,11 @@
       <c r="N43" s="16">
         <v>0.33200000000000002</v>
       </c>
-      <c r="O43" s="42">
+      <c r="O43" s="40">
         <f t="shared" si="0"/>
         <v>0.75900000000000001</v>
       </c>
-      <c r="P43" s="42">
+      <c r="P43" s="40">
         <f t="shared" si="1"/>
         <v>0.33200000000000002</v>
       </c>
@@ -4000,11 +3989,11 @@
       <c r="N44" s="16">
         <v>0.309</v>
       </c>
-      <c r="O44" s="42">
+      <c r="O44" s="40">
         <f t="shared" si="0"/>
         <v>0.63700000000000001</v>
       </c>
-      <c r="P44" s="42">
+      <c r="P44" s="40">
         <f t="shared" si="1"/>
         <v>0.309</v>
       </c>
@@ -4045,17 +4034,15 @@
       <c r="N45" s="16">
         <v>0.161</v>
       </c>
-      <c r="O45" s="42">
+      <c r="O45" s="40">
         <f t="shared" si="0"/>
         <v>1.4159999999999999</v>
       </c>
-      <c r="P45" s="42">
+      <c r="P45" s="40">
         <f t="shared" si="1"/>
         <v>0.64400000000000002</v>
       </c>
-      <c r="Q45" s="35" t="s">
-        <v>339</v>
-      </c>
+      <c r="Q45" s="33"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
@@ -4082,8 +4069,8 @@
       <c r="K46" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="L46" s="41" t="s">
-        <v>504</v>
+      <c r="L46" s="39" t="s">
+        <v>503</v>
       </c>
       <c r="M46" s="16">
         <v>3.53</v>
@@ -4091,11 +4078,11 @@
       <c r="N46" s="16">
         <v>2.97</v>
       </c>
-      <c r="O46" s="42">
+      <c r="O46" s="40">
         <f t="shared" si="0"/>
         <v>3.53</v>
       </c>
-      <c r="P46" s="42">
+      <c r="P46" s="40">
         <f t="shared" si="1"/>
         <v>2.97</v>
       </c>
@@ -4135,11 +4122,11 @@
       <c r="N47" s="16">
         <v>0.19</v>
       </c>
-      <c r="O47" s="42">
+      <c r="O47" s="40">
         <f t="shared" si="0"/>
         <v>0.83599999999999997</v>
       </c>
-      <c r="P47" s="42">
+      <c r="P47" s="40">
         <f t="shared" si="1"/>
         <v>0.38</v>
       </c>
@@ -4179,11 +4166,11 @@
       <c r="N48" s="24">
         <v>0.18</v>
       </c>
-      <c r="O48" s="42">
+      <c r="O48" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P48" s="42">
+      <c r="P48" s="40">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4225,11 +4212,11 @@
       <c r="N49" s="16">
         <v>9.8000000000000007</v>
       </c>
-      <c r="O49" s="42">
+      <c r="O49" s="40">
         <f t="shared" si="0"/>
         <v>9.8000000000000007</v>
       </c>
-      <c r="P49" s="42">
+      <c r="P49" s="40">
         <f t="shared" si="1"/>
         <v>9.8000000000000007</v>
       </c>
@@ -4269,11 +4256,11 @@
       <c r="N50" s="16">
         <v>0.42399999999999999</v>
       </c>
-      <c r="O50" s="42">
+      <c r="O50" s="40">
         <f t="shared" si="0"/>
         <v>0.72599999999999998</v>
       </c>
-      <c r="P50" s="42">
+      <c r="P50" s="40">
         <f t="shared" si="1"/>
         <v>0.42399999999999999</v>
       </c>
@@ -4282,8 +4269,8 @@
     <row r="51" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="M51" s="27"/>
       <c r="N51" s="27"/>
-      <c r="O51" s="43"/>
-      <c r="P51" s="43"/>
+      <c r="O51" s="41"/>
+      <c r="P51" s="41"/>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
@@ -4322,11 +4309,11 @@
       <c r="N52" s="16">
         <v>0.13900000000000001</v>
       </c>
-      <c r="O52" s="42">
+      <c r="O52" s="40">
         <f t="shared" si="0"/>
         <v>0.72599999999999998</v>
       </c>
-      <c r="P52" s="42">
+      <c r="P52" s="40">
         <f t="shared" si="1"/>
         <v>0.27800000000000002</v>
       </c>
@@ -4342,7 +4329,7 @@
         <v>319</v>
       </c>
       <c r="D53" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>214</v>
@@ -4368,11 +4355,11 @@
       <c r="N53" s="16">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="O53" s="42">
+      <c r="O53" s="40">
         <f t="shared" si="0"/>
         <v>0.84300000000000008</v>
       </c>
-      <c r="P53" s="42">
+      <c r="P53" s="40">
         <f t="shared" si="1"/>
         <v>0.27900000000000003</v>
       </c>
@@ -4388,13 +4375,13 @@
         <v>258</v>
       </c>
       <c r="D54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>214</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G54" t="s">
         <v>268</v>
@@ -4403,10 +4390,10 @@
         <v>242</v>
       </c>
       <c r="K54" t="s">
+        <v>505</v>
+      </c>
+      <c r="L54" s="39" t="s">
         <v>506</v>
-      </c>
-      <c r="L54" s="41" t="s">
-        <v>507</v>
       </c>
       <c r="M54" s="16">
         <v>0.28799999999999998</v>
@@ -4414,11 +4401,11 @@
       <c r="N54" s="16">
         <v>0.109</v>
       </c>
-      <c r="O54" s="42">
+      <c r="O54" s="40">
         <f t="shared" si="0"/>
         <v>0.86399999999999988</v>
       </c>
-      <c r="P54" s="42">
+      <c r="P54" s="40">
         <f t="shared" si="1"/>
         <v>0.32700000000000001</v>
       </c>
@@ -4431,7 +4418,7 @@
         <v>1</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>289</v>
@@ -4440,7 +4427,7 @@
         <v>214</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>239</v>
@@ -4450,10 +4437,10 @@
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="L55" s="41" t="s">
-        <v>508</v>
+        <v>374</v>
+      </c>
+      <c r="L55" s="39" t="s">
+        <v>507</v>
       </c>
       <c r="M55" s="23">
         <v>0.17499999999999999</v>
@@ -4461,11 +4448,11 @@
       <c r="N55" s="23">
         <v>3.9E-2</v>
       </c>
-      <c r="O55" s="42">
+      <c r="O55" s="40">
         <f t="shared" si="0"/>
         <v>0.17499999999999999</v>
       </c>
-      <c r="P55" s="42">
+      <c r="P55" s="40">
         <f t="shared" si="1"/>
         <v>3.9E-2</v>
       </c>
@@ -4497,8 +4484,8 @@
       <c r="K56" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="L56" s="41" t="s">
-        <v>509</v>
+      <c r="L56" s="39" t="s">
+        <v>508</v>
       </c>
       <c r="M56" s="23">
         <v>0.126</v>
@@ -4506,11 +4493,11 @@
       <c r="N56" s="23">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="O56" s="42">
+      <c r="O56" s="40">
         <f t="shared" si="0"/>
         <v>0.126</v>
       </c>
-      <c r="P56" s="42">
+      <c r="P56" s="40">
         <f t="shared" si="1"/>
         <v>8.5000000000000006E-2</v>
       </c>
@@ -4542,8 +4529,8 @@
       <c r="K57" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="L57" s="41" t="s">
-        <v>510</v>
+      <c r="L57" s="39" t="s">
+        <v>509</v>
       </c>
       <c r="M57" s="16">
         <v>0.13600000000000001</v>
@@ -4551,11 +4538,11 @@
       <c r="N57" s="23">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="O57" s="42">
+      <c r="O57" s="40">
         <f t="shared" si="0"/>
         <v>0.13600000000000001</v>
       </c>
-      <c r="P57" s="42">
+      <c r="P57" s="40">
         <f t="shared" si="1"/>
         <v>8.5000000000000006E-2</v>
       </c>
@@ -4587,8 +4574,8 @@
       <c r="K58" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="L58" s="41" t="s">
-        <v>511</v>
+      <c r="L58" s="39" t="s">
+        <v>510</v>
       </c>
       <c r="M58" s="23">
         <v>0.126</v>
@@ -4596,11 +4583,11 @@
       <c r="N58" s="23">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="O58" s="42">
+      <c r="O58" s="40">
         <f t="shared" si="0"/>
         <v>0.126</v>
       </c>
-      <c r="P58" s="42">
+      <c r="P58" s="40">
         <f t="shared" si="1"/>
         <v>8.5000000000000006E-2</v>
       </c>
@@ -4633,8 +4620,8 @@
       <c r="K59" t="s">
         <v>314</v>
       </c>
-      <c r="L59" s="41" t="s">
-        <v>512</v>
+      <c r="L59" s="39" t="s">
+        <v>511</v>
       </c>
       <c r="M59" s="16">
         <v>0.114</v>
@@ -4642,11 +4629,11 @@
       <c r="N59" s="16">
         <v>3.1E-2</v>
       </c>
-      <c r="O59" s="42">
+      <c r="O59" s="40">
         <f t="shared" si="0"/>
         <v>0.114</v>
       </c>
-      <c r="P59" s="42">
+      <c r="P59" s="40">
         <f t="shared" si="1"/>
         <v>3.1E-2</v>
       </c>
@@ -4659,16 +4646,16 @@
         <v>2</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>214</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>239</v>
@@ -4678,10 +4665,10 @@
       </c>
       <c r="J60" s="4"/>
       <c r="K60" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L60" s="29" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M60" s="23">
         <v>0.17499999999999999</v>
@@ -4689,11 +4676,11 @@
       <c r="N60" s="23">
         <v>3.9E-2</v>
       </c>
-      <c r="O60" s="42">
+      <c r="O60" s="40">
         <f t="shared" si="0"/>
         <v>0.35</v>
       </c>
-      <c r="P60" s="42">
+      <c r="P60" s="40">
         <f t="shared" si="1"/>
         <v>7.8E-2</v>
       </c>
@@ -4701,8 +4688,8 @@
     <row r="61" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="M61" s="27"/>
       <c r="N61" s="27"/>
-      <c r="O61" s="43"/>
-      <c r="P61" s="43"/>
+      <c r="O61" s="41"/>
+      <c r="P61" s="41"/>
     </row>
     <row r="62" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="17">
@@ -4712,7 +4699,7 @@
         <v>1</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D62" s="17" t="s">
         <v>196</v>
@@ -4742,11 +4729,11 @@
       <c r="N62" s="23">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="O62" s="42">
+      <c r="O62" s="40">
         <f t="shared" si="0"/>
         <v>0.29399999999999998</v>
       </c>
-      <c r="P62" s="42">
+      <c r="P62" s="40">
         <f t="shared" si="1"/>
         <v>9.7000000000000003E-2</v>
       </c>
@@ -4759,7 +4746,7 @@
         <v>1</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D63" s="7" t="s">
         <v>198</v>
@@ -4768,7 +4755,7 @@
         <v>87</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>239</v>
@@ -4776,10 +4763,10 @@
       <c r="H63" s="9"/>
       <c r="J63" s="4"/>
       <c r="K63" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="L63" s="41" t="s">
-        <v>513</v>
+        <v>385</v>
+      </c>
+      <c r="L63" s="39" t="s">
+        <v>512</v>
       </c>
       <c r="M63" s="23">
         <v>0.441</v>
@@ -4787,11 +4774,11 @@
       <c r="N63" s="23">
         <v>0.26</v>
       </c>
-      <c r="O63" s="42">
+      <c r="O63" s="40">
         <f t="shared" si="0"/>
         <v>0.441</v>
       </c>
-      <c r="P63" s="42">
+      <c r="P63" s="40">
         <f t="shared" si="1"/>
         <v>0.26</v>
       </c>
@@ -4799,8 +4786,8 @@
     <row r="64" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="M64" s="27"/>
       <c r="N64" s="27"/>
-      <c r="O64" s="43"/>
-      <c r="P64" s="43"/>
+      <c r="O64" s="41"/>
+      <c r="P64" s="41"/>
     </row>
     <row r="65" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="17">
@@ -4828,8 +4815,8 @@
       <c r="K65" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="L65" s="41" t="s">
-        <v>462</v>
+      <c r="L65" s="39" t="s">
+        <v>461</v>
       </c>
       <c r="M65" s="23">
         <v>0.95699999999999996</v>
@@ -4837,11 +4824,11 @@
       <c r="N65" s="23">
         <v>0.65600000000000003</v>
       </c>
-      <c r="O65" s="42">
+      <c r="O65" s="40">
         <f t="shared" si="0"/>
         <v>0.95699999999999996</v>
       </c>
-      <c r="P65" s="42">
+      <c r="P65" s="40">
         <f t="shared" si="1"/>
         <v>0.65600000000000003</v>
       </c>
@@ -4849,8 +4836,8 @@
     <row r="66" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="M66" s="27"/>
       <c r="N66" s="27"/>
-      <c r="O66" s="43"/>
-      <c r="P66" s="43"/>
+      <c r="O66" s="41"/>
+      <c r="P66" s="41"/>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" s="17">
@@ -4860,25 +4847,25 @@
         <v>1</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D67" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E67" t="s">
         <v>326</v>
       </c>
       <c r="F67" t="s">
+        <v>347</v>
+      </c>
+      <c r="G67" t="s">
+        <v>339</v>
+      </c>
+      <c r="I67" t="s">
+        <v>345</v>
+      </c>
+      <c r="K67" t="s">
         <v>348</v>
-      </c>
-      <c r="G67" t="s">
-        <v>340</v>
-      </c>
-      <c r="I67" t="s">
-        <v>346</v>
-      </c>
-      <c r="K67" t="s">
-        <v>349</v>
       </c>
       <c r="L67" s="13">
         <v>300</v>
@@ -4889,11 +4876,11 @@
       <c r="N67" s="16">
         <v>1.24</v>
       </c>
-      <c r="O67" s="42">
+      <c r="O67" s="40">
         <f t="shared" si="0"/>
         <v>1.91</v>
       </c>
-      <c r="P67" s="42">
+      <c r="P67" s="40">
         <f t="shared" si="1"/>
         <v>1.24</v>
       </c>
@@ -4912,13 +4899,13 @@
         <v>125</v>
       </c>
       <c r="J68" s="19"/>
-      <c r="M68" s="36"/>
-      <c r="N68" s="36"/>
-      <c r="O68" s="42">
+      <c r="M68" s="35"/>
+      <c r="N68" s="35"/>
+      <c r="O68" s="40">
         <f t="shared" ref="O68:O76" si="2">B68*M68</f>
         <v>0</v>
       </c>
-      <c r="P68" s="42">
+      <c r="P68" s="40">
         <f t="shared" ref="P68:P76" si="3">B68*N68</f>
         <v>0</v>
       </c>
@@ -4931,7 +4918,7 @@
         <v>1</v>
       </c>
       <c r="C69" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>58</v>
@@ -4960,11 +4947,11 @@
       <c r="N69" s="16">
         <v>0.307</v>
       </c>
-      <c r="O69" s="42">
+      <c r="O69" s="40">
         <f t="shared" si="2"/>
         <v>0.503</v>
       </c>
-      <c r="P69" s="42">
+      <c r="P69" s="40">
         <f t="shared" si="3"/>
         <v>0.307</v>
       </c>
@@ -4977,7 +4964,7 @@
         <v>1</v>
       </c>
       <c r="C70" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>126</v>
@@ -5003,11 +4990,11 @@
       <c r="N70" s="16">
         <v>1.32</v>
       </c>
-      <c r="O70" s="42">
+      <c r="O70" s="40">
         <f t="shared" si="2"/>
         <v>1.93</v>
       </c>
-      <c r="P70" s="42">
+      <c r="P70" s="40">
         <f t="shared" si="3"/>
         <v>1.32</v>
       </c>
@@ -5020,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D71" s="7" t="s">
         <v>59</v>
@@ -5028,12 +5015,12 @@
       <c r="E71" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="F71" s="38" t="s">
-        <v>372</v>
+      <c r="F71" s="37" t="s">
+        <v>371</v>
       </c>
       <c r="J71" s="4"/>
       <c r="K71" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="L71" s="13">
         <v>1351</v>
@@ -5044,11 +5031,11 @@
       <c r="N71" s="23">
         <v>2.2400000000000002</v>
       </c>
-      <c r="O71" s="42">
+      <c r="O71" s="40">
         <f t="shared" si="2"/>
         <v>2.2400000000000002</v>
       </c>
-      <c r="P71" s="42">
+      <c r="P71" s="40">
         <f t="shared" si="3"/>
         <v>2.2400000000000002</v>
       </c>
@@ -5061,7 +5048,7 @@
         <v>1</v>
       </c>
       <c r="C72" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>294</v>
@@ -5087,11 +5074,11 @@
       <c r="N72" s="16">
         <v>2.37</v>
       </c>
-      <c r="O72" s="42">
+      <c r="O72" s="40">
         <f t="shared" si="2"/>
         <v>3.45</v>
       </c>
-      <c r="P72" s="42">
+      <c r="P72" s="40">
         <f t="shared" si="3"/>
         <v>2.37</v>
       </c>
@@ -5104,7 +5091,7 @@
         <v>1</v>
       </c>
       <c r="C73" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D73" s="7" t="s">
         <v>295</v>
@@ -5125,7 +5112,7 @@
         <v>330</v>
       </c>
       <c r="L73" s="29" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="M73" s="16">
         <v>0.59499999999999997</v>
@@ -5133,11 +5120,11 @@
       <c r="N73" s="16">
         <v>0.39600000000000002</v>
       </c>
-      <c r="O73" s="42">
+      <c r="O73" s="40">
         <f t="shared" si="2"/>
         <v>0.59499999999999997</v>
       </c>
-      <c r="P73" s="42">
+      <c r="P73" s="40">
         <f t="shared" si="3"/>
         <v>0.39600000000000002</v>
       </c>
@@ -5153,17 +5140,17 @@
         <v>243</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J74" s="19"/>
       <c r="L74"/>
-      <c r="M74" s="36"/>
-      <c r="N74" s="36"/>
-      <c r="O74" s="42">
+      <c r="M74" s="35"/>
+      <c r="N74" s="35"/>
+      <c r="O74" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P74" s="42">
+      <c r="P74" s="40">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5182,19 +5169,19 @@
         <v>296</v>
       </c>
       <c r="E75" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F75" t="s">
+        <v>354</v>
+      </c>
+      <c r="G75" t="s">
         <v>355</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
+        <v>357</v>
+      </c>
+      <c r="K75" t="s">
         <v>356</v>
-      </c>
-      <c r="H75" t="s">
-        <v>358</v>
-      </c>
-      <c r="K75" t="s">
-        <v>357</v>
       </c>
       <c r="L75" s="13">
         <v>4400</v>
@@ -5205,11 +5192,11 @@
       <c r="N75" s="16">
         <v>0.20499999999999999</v>
       </c>
-      <c r="O75" s="42">
+      <c r="O75" s="40">
         <f t="shared" si="2"/>
         <v>0.27100000000000002</v>
       </c>
-      <c r="P75" s="42">
+      <c r="P75" s="40">
         <f t="shared" si="3"/>
         <v>0.20499999999999999</v>
       </c>
@@ -5225,38 +5212,38 @@
         <v>263</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E76" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="F76" s="2" t="s">
+      <c r="G76" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="G76" s="2" t="s">
-        <v>352</v>
-      </c>
       <c r="H76" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J76" s="19"/>
       <c r="K76" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="L76" s="37">
+        <v>352</v>
+      </c>
+      <c r="L76" s="36">
         <v>4300</v>
       </c>
-      <c r="M76" s="36">
+      <c r="M76" s="35">
         <v>0.27100000000000002</v>
       </c>
-      <c r="N76" s="36">
+      <c r="N76" s="35">
         <v>0.20499999999999999</v>
       </c>
-      <c r="O76" s="42">
+      <c r="O76" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P76" s="42">
+      <c r="P76" s="40">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5272,6 +5259,10 @@
       <c r="O79" s="1">
         <f>SUM(O3:O76)</f>
         <v>51.401999999999994</v>
+      </c>
+      <c r="P79" s="40">
+        <f>SUM(P3:P76)</f>
+        <v>37.367999999999995</v>
       </c>
     </row>
     <row r="81" spans="4:16" x14ac:dyDescent="0.35">
